--- a/Pacific_Elite_Rides_Earnings.xlsx
+++ b/Pacific_Elite_Rides_Earnings.xlsx
@@ -1,17 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/berdnikovandrii/Documents/Claude/Projects/New beginning - Transport LLC/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E582CEAC-B2CB-2144-A7B4-369A685065A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Earnings" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Earnings" sheetId="1" r:id="rId1"/>
+    <sheet name="Private Rides" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -19,48 +36,156 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Legacy entry from before the Fleet/Mine split (no per-ride detail on file). Assumed "Mine" — adjust if this was actually a fleet-vehicle ride.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t xml:space="preserve">PACIFIC ELITE RIDES — Earnings Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uber ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lyft ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private Rides ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+  <si>
+    <t>PACIFIC ELITE RIDES — Earnings Tracker</t>
+  </si>
+  <si>
+    <t>Period Start</t>
+  </si>
+  <si>
+    <t>Period End</t>
+  </si>
+  <si>
+    <t>Uber ($)</t>
+  </si>
+  <si>
+    <t>Lyft ($)</t>
+  </si>
+  <si>
+    <t>Private Rides – Fleet Fare ($)</t>
+  </si>
+  <si>
+    <t>Private Rides – Fleet Tips ($)</t>
+  </si>
+  <si>
+    <t>Private Rides – Mine ($)</t>
+  </si>
+  <si>
+    <t>Total ($)</t>
+  </si>
+  <si>
+    <t>Fleet Owes Me ($)</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>PACIFIC ELITE RIDES — Private Rides Detail</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Type (Fleet/Mine)</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Route</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Fare ($)</t>
+  </si>
+  <si>
+    <t>Tip ($)</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>Fleet</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>San Diego → Los Angeles (SoFi Stadium), round trip</t>
+  </si>
+  <si>
+    <t>Tip received directly</t>
+  </si>
+  <si>
+    <t>Дуже гарний приватний райд</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>Mine</t>
+  </si>
+  <si>
+    <t>Marina Bay → Airport</t>
+  </si>
+  <si>
+    <t>Coronado → Airport</t>
+  </si>
+  <si>
+    <t>Barrio Logan → Coronado</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>Oceanside Bar → Hotel</t>
+  </si>
+  <si>
+    <t>How to use: add one row per private ride directly above the TOTAL row so totals auto-extend. Type must be exactly "Fleet" or "Mine" — it drives the Fleet/Mine split on the Earnings tab. Tips are assumed to always come directly to Andrii (even on Fleet rides) and are excluded from the Fleet Owes Me settlement — only the Fare portion of Fleet rides counts toward that. Fill Date, Period Start (must match a Period Start on the Earnings tab), Client, Route, Vehicle, Fare, Tip, Payment, Notes.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,47 +194,35 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Cambria"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -133,93 +246,32 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="1">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFB7B7B7"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7B7B7"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7B7B7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -236,7 +288,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFB7B7B7"/>
+      <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -278,13 +330,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -326,12 +394,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -360,7 +428,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -381,7 +449,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -432,7 +500,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -450,39 +518,35 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="4" width="12" customWidth="1"/>
+    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -501,59 +565,403 @@
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
         <v>2254</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="3">
         <v>307</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
         <v>150</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <f aca="false">SUM(C4:E4)</f>
+      <c r="H4" s="3">
+        <f>SUM(C4:G4)</f>
         <v>2711</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <f aca="false">SUM(C4)</f>
-        <v>2254</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <f aca="false">SUM(D4)</f>
-        <v>307</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <f aca="false">SUM(E4)</f>
-        <v>150</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <f aca="false">SUM(F4)</f>
-        <v>2711</v>
+      <c r="I4" s="3">
+        <f>(C4+E4)-750</f>
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>663</v>
+      </c>
+      <c r="D5" s="3">
+        <v>163</v>
+      </c>
+      <c r="E5" s="3">
+        <f>SUMIFS('Private Rides'!G:G,'Private Rides'!B:B,A5,'Private Rides'!C:C,"Fleet")</f>
+        <v>665</v>
+      </c>
+      <c r="F5" s="3">
+        <f>SUMIFS('Private Rides'!H:H,'Private Rides'!B:B,A5,'Private Rides'!C:C,"Fleet")</f>
+        <v>350</v>
+      </c>
+      <c r="G5" s="3">
+        <f>SUMIFS('Private Rides'!I:I,'Private Rides'!B:B,A5,'Private Rides'!C:C,"Mine")</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <f>SUM(C5:G5)</f>
+        <v>1841</v>
+      </c>
+      <c r="I5" s="3">
+        <f>(C5+E5)-750</f>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1754</v>
+      </c>
+      <c r="D6" s="3">
+        <v>264</v>
+      </c>
+      <c r="E6" s="3">
+        <f>SUMIFS('Private Rides'!G:G,'Private Rides'!B:B,A6,'Private Rides'!C:C,"Fleet")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <f>SUMIFS('Private Rides'!H:H,'Private Rides'!B:B,A6,'Private Rides'!C:C,"Fleet")</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <f>SUMIFS('Private Rides'!I:I,'Private Rides'!B:B,A6,'Private Rides'!C:C,"Mine")</f>
+        <v>260</v>
+      </c>
+      <c r="H6" s="3">
+        <f>SUM(C6:G6)</f>
+        <v>2278</v>
+      </c>
+      <c r="I6" s="3">
+        <f>(C6+E6)-750</f>
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <f t="shared" ref="C7:I7" si="0">SUM(C4:C6)</f>
+        <v>4671</v>
+      </c>
+      <c r="D7" s="5">
+        <f t="shared" si="0"/>
+        <v>734</v>
+      </c>
+      <c r="E7" s="5">
+        <f t="shared" si="0"/>
+        <v>665</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="0"/>
+        <v>410</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="0"/>
+        <v>6830</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="0"/>
+        <v>3086</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="3">
+        <v>665</v>
+      </c>
+      <c r="H4" s="3">
+        <v>350</v>
+      </c>
+      <c r="I4" s="3">
+        <f>G4+H4</f>
+        <v>1015</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3">
+        <v>55</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <f>G5+H5</f>
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3">
+        <v>65</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <f>G6+H6</f>
+        <v>65</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="3">
+        <v>40</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <f>G7+H7</f>
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <f>G8+H8</f>
+        <v>100</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="5">
+        <f>SUM(G4:G8)</f>
+        <v>925</v>
+      </c>
+      <c r="H10" s="5">
+        <f>SUM(H4:H8)</f>
+        <v>350</v>
+      </c>
+      <c r="I10" s="5">
+        <f>SUM(I4:I8)</f>
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>